--- a/traobang.be/traobang.be/Templates/ImportSlide.xlsx
+++ b/traobang.be/traobang.be/Templates/ImportSlide.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\traobang\traobang.be\traobang.be\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7616C909-1583-48BF-BCC3-5116CDE95837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4518586C-5382-4FB0-85C0-95BEC3375C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>STT</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Khoa</t>
+  </si>
+  <si>
+    <t>QR Tên Khoa</t>
+  </si>
+  <si>
+    <t>QR Họ tên</t>
   </si>
 </sst>
 </file>
@@ -112,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,13 +141,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -424,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -443,7 +463,7 @@
     <col min="17" max="17" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,6 +514,12 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
